--- a/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Medication.xlsx
+++ b/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Medication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7294" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7291" uniqueCount="723">
   <si>
     <t>Property</t>
   </si>
@@ -445,7 +445,7 @@
     <t>Medication.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -483,7 +483,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -517,7 +517,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -560,7 +560,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -595,10 +595,6 @@
     <t>Medication.contained</t>
   </si>
   <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
     <t xml:space="preserve">Medication {https://gematik.de/fhir/epa-medication/StructureDefinition/epa-medication-pharmaceutical-product|https://gematik.de/fhir/epa-medication/StructureDefinition/epa-medication-pzn-ingredient}
 </t>
   </si>
@@ -615,16 +611,16 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t>Medication.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>Medication.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
   </si>
   <si>
     <t>Medication.extension:rxPrescriptionProcessIdentifier</t>
@@ -651,9 +647,6 @@
   <si>
     <t xml:space="preserve">Extension {https://gematik.de/fhir/epa-medication/StructureDefinition/medication-id-vaccine-extension}
 </t>
-  </si>
-  <si>
-    <t>Optional Extensions Element</t>
   </si>
   <si>
     <t>Indicator of whether this is a vaccine.</t>
@@ -907,6 +900,9 @@
 </t>
   </si>
   <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
     <t>Optional Extension Element - found in all resources.</t>
   </si>
   <si>
@@ -1070,10 +1066,10 @@
 </t>
   </si>
   <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
+    <t>Business identifier for this medication</t>
+  </si>
+  <si>
+    <t>Business identifier for this medication.</t>
   </si>
   <si>
     <t>The serial number could be included as an identifier.</t>
@@ -1118,7 +1114,7 @@
     <t>A coded concept that defines the type of a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>coding.code = //element(*,MedicationType)/DrugCoded/ProductCode@@ -1338,7 +1334,7 @@
     <t>Medication.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1408,7 +1404,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1465,7 +1461,7 @@
     <t>A coded concept defining the form of a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-form-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-form-codes|4.0.1</t>
   </si>
   <si>
     <t>coding.code =  //element(*,DrugCodedType)/FormCode@@ -1915,7 +1911,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance|Medication)</t>
+Reference(Substance|4.0.1|Medication|4.0.1)</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -2601,7 +2597,7 @@
     <col min="1" max="1" width="64.22265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="45.42578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="25.1328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -4360,7 +4356,7 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4379,16 +4375,16 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4438,7 +4434,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4453,10 +4449,10 @@
         <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>190</v>
+        <v>86</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
@@ -4467,10 +4463,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4499,7 +4495,7 @@
         <v>110</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>112</v>
@@ -4552,7 +4548,7 @@
         <v>115</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4570,7 +4566,7 @@
         <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>78</v>
@@ -4581,16 +4577,16 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C18" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="B18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>195</v>
-      </c>
       <c r="D18" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4609,17 +4605,15 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4668,7 +4662,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4677,7 +4671,7 @@
         <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>117</v>
@@ -4686,7 +4680,7 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -4697,13 +4691,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>78</v>
@@ -4725,13 +4719,13 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4782,7 +4776,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4791,7 +4785,7 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>117</v>
@@ -4800,7 +4794,7 @@
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
@@ -4811,10 +4805,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4923,10 +4917,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4952,10 +4946,10 @@
         <v>109</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5035,10 +5029,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5064,13 +5058,13 @@
         <v>130</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5078,7 +5072,7 @@
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>78</v>
@@ -5120,7 +5114,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>88</v>
@@ -5138,7 +5132,7 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
@@ -5149,10 +5143,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5175,13 +5169,13 @@
         <v>78</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5232,7 +5226,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -5250,7 +5244,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -5261,13 +5255,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
@@ -5289,13 +5283,13 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5346,7 +5340,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5355,7 +5349,7 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>117</v>
@@ -5364,7 +5358,7 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -5375,10 +5369,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5487,10 +5481,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5516,10 +5510,10 @@
         <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5599,10 +5593,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5628,13 +5622,13 @@
         <v>130</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5642,7 +5636,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>78</v>
@@ -5684,7 +5678,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>88</v>
@@ -5702,7 +5696,7 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5713,10 +5707,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5742,10 +5736,10 @@
         <v>142</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5772,11 +5766,11 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
@@ -5794,7 +5788,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5812,7 +5806,7 @@
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5823,10 +5817,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5935,10 +5929,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6049,10 +6043,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6078,16 +6072,16 @@
         <v>130</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -6136,7 +6130,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -6154,21 +6148,21 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6194,13 +6188,13 @@
         <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6250,7 +6244,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6268,21 +6262,21 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6308,14 +6302,14 @@
         <v>167</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -6364,7 +6358,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6382,21 +6376,21 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6422,16 +6416,16 @@
         <v>102</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -6480,7 +6474,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6498,21 +6492,21 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6535,19 +6529,19 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -6596,7 +6590,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6614,24 +6608,24 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>78</v>
@@ -6653,13 +6647,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6710,7 +6704,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6719,7 +6713,7 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>117</v>
@@ -6728,7 +6722,7 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6739,10 +6733,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6851,10 +6845,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6965,10 +6959,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6994,13 +6988,13 @@
         <v>130</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7008,7 +7002,7 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>78</v>
@@ -7050,7 +7044,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>88</v>
@@ -7068,7 +7062,7 @@
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -7079,10 +7073,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7108,10 +7102,10 @@
         <v>167</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7138,11 +7132,11 @@
         <v>78</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>78</v>
@@ -7160,7 +7154,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -7178,7 +7172,7 @@
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -7189,13 +7183,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C41" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>78</v>
@@ -7217,13 +7211,13 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7274,7 +7268,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7283,7 +7277,7 @@
         <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>117</v>
@@ -7292,7 +7286,7 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7303,10 +7297,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7415,14 +7409,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7444,14 +7438,12 @@
         <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -7518,7 +7510,7 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -7529,10 +7521,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7558,13 +7550,13 @@
         <v>130</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7572,7 +7564,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>78</v>
@@ -7614,7 +7606,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -7632,7 +7624,7 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7643,10 +7635,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7672,10 +7664,10 @@
         <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7699,7 +7691,7 @@
         <v>78</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="X45" t="s" s="2">
         <v>78</v>
@@ -7726,7 +7718,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7744,7 +7736,7 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7755,13 +7747,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C46" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>78</v>
@@ -7783,13 +7775,13 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7840,7 +7832,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7849,7 +7841,7 @@
         <v>80</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>117</v>
@@ -7858,7 +7850,7 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7869,10 +7861,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7981,10 +7973,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8010,10 +8002,10 @@
         <v>109</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8093,10 +8085,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8122,13 +8114,13 @@
         <v>130</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8136,7 +8128,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>78</v>
@@ -8178,7 +8170,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>88</v>
@@ -8196,7 +8188,7 @@
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -8207,10 +8199,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8236,10 +8228,10 @@
         <v>102</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8263,7 +8255,7 @@
         <v>78</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="X50" t="s" s="2">
         <v>78</v>
@@ -8290,7 +8282,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8308,7 +8300,7 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -8319,16 +8311,16 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="B51" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>316</v>
-      </c>
       <c r="D51" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8347,17 +8339,15 @@
         <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -8406,7 +8396,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8415,7 +8405,7 @@
         <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>117</v>
@@ -8424,7 +8414,7 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
@@ -8435,10 +8425,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8464,16 +8454,16 @@
         <v>109</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -8522,7 +8512,7 @@
         <v>115</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8540,7 +8530,7 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
@@ -8551,10 +8541,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8577,16 +8567,16 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8624,7 +8614,7 @@
         <v>78</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -8634,7 +8624,7 @@
         <v>115</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8652,24 +8642,24 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C54" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>78</v>
@@ -8691,16 +8681,16 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8711,7 +8701,7 @@
         <v>78</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>78</v>
@@ -8750,7 +8740,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8768,24 +8758,24 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>78</v>
@@ -8807,16 +8797,16 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8827,7 +8817,7 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>78</v>
@@ -8866,7 +8856,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8884,21 +8874,21 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8921,16 +8911,16 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8959,11 +8949,11 @@
         <v>157</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="Z56" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8980,7 +8970,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8995,24 +8985,24 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AL56" t="s" s="2">
+      <c r="AM56" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>355</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9121,10 +9111,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9235,10 +9225,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9264,16 +9254,16 @@
         <v>142</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -9310,7 +9300,7 @@
         <v>78</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
@@ -9320,7 +9310,7 @@
         <v>115</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9338,24 +9328,24 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>365</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C60" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>78</v>
@@ -9380,16 +9370,16 @@
         <v>142</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9399,7 +9389,7 @@
         <v>78</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>78</v>
@@ -9438,7 +9428,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9456,21 +9446,21 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>365</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9579,10 +9569,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9693,10 +9683,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9722,16 +9712,16 @@
         <v>130</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9780,7 +9770,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9798,21 +9788,21 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9838,13 +9828,13 @@
         <v>102</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9894,7 +9884,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9912,21 +9902,21 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9952,14 +9942,14 @@
         <v>167</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -10008,7 +9998,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10026,21 +10016,21 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10066,16 +10056,16 @@
         <v>102</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -10124,7 +10114,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10142,21 +10132,21 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10179,19 +10169,19 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -10240,7 +10230,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10258,24 +10248,24 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C68" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>78</v>
@@ -10300,16 +10290,16 @@
         <v>142</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10319,7 +10309,7 @@
         <v>78</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>78</v>
@@ -10358,7 +10348,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10376,21 +10366,21 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>365</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10499,10 +10489,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10613,10 +10603,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10642,16 +10632,16 @@
         <v>130</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10700,7 +10690,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10718,21 +10708,21 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10758,13 +10748,13 @@
         <v>102</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10814,7 +10804,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10832,21 +10822,21 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10872,14 +10862,14 @@
         <v>167</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10928,7 +10918,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10946,21 +10936,21 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10986,16 +10976,16 @@
         <v>102</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -11044,7 +11034,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11062,21 +11052,21 @@
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11099,19 +11089,19 @@
         <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -11160,7 +11150,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11178,24 +11168,24 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C76" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>78</v>
@@ -11220,16 +11210,16 @@
         <v>142</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -11239,7 +11229,7 @@
         <v>78</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>78</v>
@@ -11278,7 +11268,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11296,21 +11286,21 @@
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>365</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11419,10 +11409,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11533,10 +11523,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11562,16 +11552,16 @@
         <v>130</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11620,7 +11610,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11638,21 +11628,21 @@
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11678,13 +11668,13 @@
         <v>102</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11734,7 +11724,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11752,21 +11742,21 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11792,14 +11782,14 @@
         <v>167</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
@@ -11848,7 +11838,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11866,21 +11856,21 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11906,16 +11896,16 @@
         <v>102</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -11964,7 +11954,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11982,21 +11972,21 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12019,19 +12009,19 @@
         <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -12080,7 +12070,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12098,21 +12088,21 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12138,16 +12128,16 @@
         <v>102</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -12196,7 +12186,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12214,21 +12204,21 @@
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>412</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12254,13 +12244,13 @@
         <v>167</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12286,14 +12276,14 @@
         <v>78</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>418</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12310,7 +12300,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12328,7 +12318,7 @@
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
@@ -12339,10 +12329,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12365,16 +12355,16 @@
         <v>89</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12424,7 +12414,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12436,27 +12426,27 @@
         <v>150</v>
       </c>
       <c r="AJ86" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AK86" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AK86" t="s" s="2">
+      <c r="AL86" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AL86" t="s" s="2">
+      <c r="AM86" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AM86" t="s" s="2">
+      <c r="AN86" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>429</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12565,10 +12555,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12679,10 +12669,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12708,13 +12698,13 @@
         <v>102</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12764,16 +12754,16 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI89" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>100</v>
@@ -12782,7 +12772,7 @@
         <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -12793,10 +12783,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12822,13 +12812,13 @@
         <v>130</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12857,28 +12847,28 @@
         <v>146</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="Z90" t="s" s="2">
+      <c r="AA90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12896,7 +12886,7 @@
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12907,10 +12897,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12933,16 +12923,16 @@
         <v>89</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12992,7 +12982,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13010,21 +13000,21 @@
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13050,13 +13040,13 @@
         <v>102</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13106,7 +13096,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13124,7 +13114,7 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -13135,10 +13125,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13161,16 +13151,16 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13199,11 +13189,11 @@
         <v>157</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="Z93" t="s" s="2">
-        <v>461</v>
-      </c>
       <c r="AA93" t="s" s="2">
         <v>78</v>
       </c>
@@ -13220,7 +13210,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13235,24 +13225,24 @@
         <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AL93" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AL93" t="s" s="2">
+      <c r="AM93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>464</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13361,10 +13351,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13475,10 +13465,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13504,16 +13494,16 @@
         <v>142</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>78</v>
@@ -13550,7 +13540,7 @@
         <v>78</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AC96" s="2"/>
       <c r="AD96" t="s" s="2">
@@ -13560,7 +13550,7 @@
         <v>115</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13578,24 +13568,24 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>365</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C97" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>78</v>
@@ -13620,16 +13610,16 @@
         <v>142</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M97" t="s" s="2">
-        <v>360</v>
-      </c>
       <c r="N97" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -13639,7 +13629,7 @@
         <v>78</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>78</v>
@@ -13654,11 +13644,11 @@
         <v>78</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>78</v>
@@ -13676,7 +13666,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13694,21 +13684,21 @@
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>365</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13817,10 +13807,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13931,10 +13921,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B100" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13960,16 +13950,16 @@
         <v>130</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -14018,7 +14008,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14036,21 +14026,21 @@
         <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14076,13 +14066,13 @@
         <v>102</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14132,7 +14122,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14150,21 +14140,21 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B102" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14190,14 +14180,14 @@
         <v>167</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -14246,7 +14236,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14264,21 +14254,21 @@
         <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B103" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14304,16 +14294,16 @@
         <v>102</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14362,7 +14352,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14380,21 +14370,21 @@
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14417,19 +14407,19 @@
         <v>89</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -14478,7 +14468,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14496,21 +14486,21 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14536,16 +14526,16 @@
         <v>102</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -14594,7 +14584,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14612,21 +14602,21 @@
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>412</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14649,16 +14639,16 @@
         <v>89</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14708,7 +14698,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14720,27 +14710,27 @@
         <v>150</v>
       </c>
       <c r="AJ106" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL106" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AK106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>494</v>
-      </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14849,10 +14839,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14963,10 +14953,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14989,16 +14979,16 @@
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15028,25 +15018,25 @@
       </c>
       <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF109" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15058,27 +15048,27 @@
         <v>150</v>
       </c>
       <c r="AJ109" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL109" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AK109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL109" t="s" s="2">
+      <c r="AM109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN109" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>506</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15187,10 +15177,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15301,13 +15291,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C112" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>78</v>
@@ -15329,13 +15319,13 @@
         <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15395,7 +15385,7 @@
         <v>80</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>117</v>
@@ -15404,7 +15394,7 @@
         <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -15415,10 +15405,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15527,10 +15517,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15556,10 +15546,10 @@
         <v>109</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15639,10 +15629,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15668,13 +15658,13 @@
         <v>130</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N115" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15682,7 +15672,7 @@
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>78</v>
@@ -15724,7 +15714,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>88</v>
@@ -15742,7 +15732,7 @@
         <v>78</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>78</v>
@@ -15753,10 +15743,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B116" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15782,10 +15772,10 @@
         <v>102</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15809,7 +15799,7 @@
         <v>78</v>
       </c>
       <c r="W116" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="X116" t="s" s="2">
         <v>78</v>
@@ -15836,7 +15826,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15854,7 +15844,7 @@
         <v>78</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>78</v>
@@ -15865,13 +15855,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C117" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>78</v>
@@ -15893,13 +15883,13 @@
         <v>78</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -15959,7 +15949,7 @@
         <v>80</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>117</v>
@@ -15968,7 +15958,7 @@
         <v>78</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>78</v>
@@ -15979,10 +15969,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16091,10 +16081,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16120,10 +16110,10 @@
         <v>109</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16203,10 +16193,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16232,13 +16222,13 @@
         <v>130</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N120" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16246,7 +16236,7 @@
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>78</v>
@@ -16288,7 +16278,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>88</v>
@@ -16306,7 +16296,7 @@
         <v>78</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>78</v>
@@ -16317,10 +16307,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16346,10 +16336,10 @@
         <v>102</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16373,7 +16363,7 @@
         <v>78</v>
       </c>
       <c r="W121" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="X121" t="s" s="2">
         <v>78</v>
@@ -16400,7 +16390,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16418,7 +16408,7 @@
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>78</v>
@@ -16429,10 +16419,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16455,19 +16445,19 @@
         <v>89</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="N122" t="s" s="2">
+      <c r="O122" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -16516,7 +16506,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16534,21 +16524,21 @@
         <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>542</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16574,65 +16564,65 @@
         <v>167</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q123" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="P123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q123" t="s" s="2">
+      <c r="R123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="Y123" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="R123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y123" t="s" s="2">
+      <c r="Z123" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="Z123" t="s" s="2">
+      <c r="AA123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF123" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16650,21 +16640,21 @@
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>552</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16690,16 +16680,16 @@
         <v>102</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O124" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -16748,7 +16738,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16766,21 +16756,21 @@
         <v>78</v>
       </c>
       <c r="AL124" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>559</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16806,16 +16796,16 @@
         <v>130</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="N125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>78</v>
@@ -16864,16 +16854,16 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI125" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>100</v>
@@ -16882,21 +16872,21 @@
         <v>78</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16922,16 +16912,16 @@
         <v>167</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>78</v>
@@ -16980,7 +16970,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -16998,21 +16988,21 @@
         <v>78</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17035,16 +17025,16 @@
         <v>89</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="M127" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="N127" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17074,7 +17064,7 @@
       </c>
       <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>78</v>
@@ -17092,7 +17082,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17104,27 +17094,27 @@
         <v>150</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17233,10 +17223,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17347,10 +17337,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17373,19 +17363,19 @@
         <v>89</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L130" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="L130" t="s" s="2">
+      <c r="M130" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="N130" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="N130" t="s" s="2">
+      <c r="O130" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>78</v>
@@ -17434,7 +17424,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17452,21 +17442,21 @@
         <v>78</v>
       </c>
       <c r="AL130" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN130" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>542</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17492,65 +17482,65 @@
         <v>167</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="P131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q131" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="P131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q131" t="s" s="2">
+      <c r="R131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="Y131" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="R131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y131" t="s" s="2">
+      <c r="Z131" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="Z131" t="s" s="2">
+      <c r="AA131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF131" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17568,21 +17558,21 @@
         <v>78</v>
       </c>
       <c r="AL131" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN131" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>552</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17608,16 +17598,16 @@
         <v>102</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O132" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>78</v>
@@ -17666,7 +17656,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17684,21 +17674,21 @@
         <v>78</v>
       </c>
       <c r="AL132" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN132" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>559</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17724,16 +17714,16 @@
         <v>130</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="N133" t="s" s="2">
+      <c r="O133" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -17782,16 +17772,16 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI133" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>100</v>
@@ -17800,21 +17790,21 @@
         <v>78</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17840,16 +17830,16 @@
         <v>167</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -17898,7 +17888,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17916,21 +17906,21 @@
         <v>78</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17953,16 +17943,16 @@
         <v>78</v>
       </c>
       <c r="K135" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="L135" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="L135" t="s" s="2">
+      <c r="M135" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="N135" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18012,7 +18002,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18030,7 +18020,7 @@
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>78</v>
@@ -18041,10 +18031,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18153,10 +18143,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18267,13 +18257,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C138" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="C138" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>78</v>
@@ -18295,13 +18285,13 @@
         <v>78</v>
       </c>
       <c r="K138" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -18361,7 +18351,7 @@
         <v>80</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>117</v>
@@ -18370,7 +18360,7 @@
         <v>78</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>78</v>
@@ -18381,14 +18371,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -18410,16 +18400,16 @@
         <v>109</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="N139" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>78</v>
@@ -18468,7 +18458,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -18486,7 +18476,7 @@
         <v>78</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>78</v>
@@ -18497,10 +18487,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18523,17 +18513,17 @@
         <v>78</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L140" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="M140" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>78</v>
@@ -18570,17 +18560,17 @@
         <v>78</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AC140" s="2"/>
       <c r="AD140" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>88</v>
@@ -18595,27 +18585,27 @@
         <v>100</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AL140" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN140" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AM140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>612</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C141" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="C141" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>78</v>
@@ -18637,17 +18627,17 @@
         <v>78</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>78</v>
@@ -18696,7 +18686,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>88</v>
@@ -18711,24 +18701,24 @@
         <v>100</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AL141" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN141" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AM141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN141" t="s" s="2">
-        <v>612</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B142" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18837,10 +18827,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B143" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18951,10 +18941,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B144" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18980,16 +18970,16 @@
         <v>142</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M144" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M144" t="s" s="2">
+      <c r="N144" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="N144" t="s" s="2">
+      <c r="O144" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>78</v>
@@ -19026,7 +19016,7 @@
         <v>78</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AC144" s="2"/>
       <c r="AD144" t="s" s="2">
@@ -19036,7 +19026,7 @@
         <v>115</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -19054,24 +19044,24 @@
         <v>78</v>
       </c>
       <c r="AL144" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN144" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN144" t="s" s="2">
-        <v>365</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>78</v>
@@ -19096,16 +19086,16 @@
         <v>142</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M145" t="s" s="2">
+      <c r="N145" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="N145" t="s" s="2">
+      <c r="O145" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -19115,7 +19105,7 @@
         <v>78</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>78</v>
@@ -19154,7 +19144,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -19172,21 +19162,21 @@
         <v>78</v>
       </c>
       <c r="AL145" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN145" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AM145" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN145" t="s" s="2">
-        <v>365</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B146" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19295,10 +19285,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="B147" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="B147" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19409,10 +19399,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="B148" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="B148" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19438,16 +19428,16 @@
         <v>130</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N148" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="O148" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>78</v>
@@ -19496,7 +19486,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -19514,21 +19504,21 @@
         <v>78</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B149" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="B149" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19554,13 +19544,13 @@
         <v>102</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -19610,7 +19600,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -19628,21 +19618,21 @@
         <v>78</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B150" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19668,14 +19658,14 @@
         <v>167</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>78</v>
@@ -19724,7 +19714,7 @@
         <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -19742,21 +19732,21 @@
         <v>78</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B151" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19782,16 +19772,16 @@
         <v>102</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N151" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="O151" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>78</v>
@@ -19840,7 +19830,7 @@
         <v>78</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -19858,21 +19848,21 @@
         <v>78</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="B152" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19895,19 +19885,19 @@
         <v>89</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N152" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M152" t="s" s="2">
+      <c r="O152" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>78</v>
@@ -19956,7 +19946,7 @@
         <v>78</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -19974,24 +19964,24 @@
         <v>78</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D153" t="s" s="2">
         <v>78</v>
@@ -20016,16 +20006,16 @@
         <v>142</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="N153" t="s" s="2">
+      <c r="O153" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>78</v>
@@ -20035,7 +20025,7 @@
         <v>78</v>
       </c>
       <c r="S153" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="T153" t="s" s="2">
         <v>78</v>
@@ -20074,7 +20064,7 @@
         <v>78</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -20092,21 +20082,21 @@
         <v>78</v>
       </c>
       <c r="AL153" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN153" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>365</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20215,10 +20205,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20329,10 +20319,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20358,16 +20348,16 @@
         <v>130</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N156" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="O156" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>78</v>
@@ -20416,7 +20406,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -20434,21 +20424,21 @@
         <v>78</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20474,13 +20464,13 @@
         <v>102</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N157" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -20530,7 +20520,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -20548,21 +20538,21 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20588,14 +20578,14 @@
         <v>167</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>78</v>
@@ -20644,7 +20634,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -20662,21 +20652,21 @@
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20702,16 +20692,16 @@
         <v>102</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N159" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="O159" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
@@ -20760,7 +20750,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -20778,21 +20768,21 @@
         <v>78</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20815,19 +20805,19 @@
         <v>89</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N160" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M160" t="s" s="2">
+      <c r="O160" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>78</v>
@@ -20876,7 +20866,7 @@
         <v>78</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -20894,24 +20884,24 @@
         <v>78</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>78</v>
@@ -20936,16 +20926,16 @@
         <v>142</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M161" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M161" t="s" s="2">
+      <c r="N161" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="N161" t="s" s="2">
+      <c r="O161" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>78</v>
@@ -20955,7 +20945,7 @@
         <v>78</v>
       </c>
       <c r="S161" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="T161" t="s" s="2">
         <v>78</v>
@@ -20994,7 +20984,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -21012,21 +21002,21 @@
         <v>78</v>
       </c>
       <c r="AL161" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AM161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN161" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AM161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN161" t="s" s="2">
-        <v>365</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21135,10 +21125,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21249,10 +21239,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21278,16 +21268,16 @@
         <v>130</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M164" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N164" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="O164" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>78</v>
@@ -21336,7 +21326,7 @@
         <v>78</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -21354,21 +21344,21 @@
         <v>78</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21394,13 +21384,13 @@
         <v>102</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M165" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N165" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -21450,7 +21440,7 @@
         <v>78</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -21468,21 +21458,21 @@
         <v>78</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21508,14 +21498,14 @@
         <v>167</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>78</v>
@@ -21564,7 +21554,7 @@
         <v>78</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -21582,21 +21572,21 @@
         <v>78</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21622,16 +21612,16 @@
         <v>102</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N167" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="O167" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>78</v>
@@ -21680,7 +21670,7 @@
         <v>78</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -21698,21 +21688,21 @@
         <v>78</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21735,19 +21725,19 @@
         <v>89</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N168" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>78</v>
@@ -21796,7 +21786,7 @@
         <v>78</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -21814,21 +21804,21 @@
         <v>78</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AM168" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B169" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="B169" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21854,16 +21844,16 @@
         <v>102</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M169" t="s" s="2">
+      <c r="N169" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="N169" t="s" s="2">
+      <c r="O169" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>78</v>
@@ -21912,7 +21902,7 @@
         <v>78</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -21930,24 +21920,24 @@
         <v>78</v>
       </c>
       <c r="AL169" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AM169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN169" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AM169" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN169" t="s" s="2">
-        <v>412</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C170" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="B170" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="C170" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="D170" t="s" s="2">
         <v>78</v>
@@ -21969,19 +21959,19 @@
         <v>78</v>
       </c>
       <c r="K170" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="L170" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="L170" t="s" s="2">
+      <c r="M170" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="M170" t="s" s="2">
+      <c r="N170" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="N170" t="s" s="2">
-        <v>661</v>
-      </c>
       <c r="O170" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>78</v>
@@ -22030,7 +22020,7 @@
         <v>78</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>88</v>
@@ -22045,24 +22035,24 @@
         <v>100</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AL170" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AM170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN170" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AM170" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN170" t="s" s="2">
-        <v>612</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22085,17 +22075,17 @@
         <v>78</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="M171" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>78</v>
@@ -22144,7 +22134,7 @@
         <v>78</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
@@ -22162,7 +22152,7 @@
         <v>78</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>78</v>
@@ -22173,10 +22163,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22199,16 +22189,16 @@
         <v>78</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="M172" t="s" s="2">
-        <v>669</v>
-      </c>
       <c r="N172" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -22258,7 +22248,7 @@
         <v>78</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -22270,27 +22260,27 @@
         <v>150</v>
       </c>
       <c r="AJ172" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AK172" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AL172" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AK172" t="s" s="2">
+      <c r="AM172" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN172" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="AL172" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AM172" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN172" t="s" s="2">
-        <v>671</v>
       </c>
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22399,10 +22389,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22513,13 +22503,13 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="C175" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="C175" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="D175" t="s" s="2">
         <v>78</v>
@@ -22541,13 +22531,13 @@
         <v>78</v>
       </c>
       <c r="K175" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="L175" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="L175" t="s" s="2">
+      <c r="M175" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="M175" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -22607,7 +22597,7 @@
         <v>80</v>
       </c>
       <c r="AI175" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ175" t="s" s="2">
         <v>117</v>
@@ -22616,7 +22606,7 @@
         <v>78</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>78</v>
@@ -22627,10 +22617,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="B176" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22739,10 +22729,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="B177" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>682</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22768,10 +22758,10 @@
         <v>109</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -22851,10 +22841,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="B178" t="s" s="2">
         <v>683</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>684</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22880,13 +22870,13 @@
         <v>130</v>
       </c>
       <c r="L178" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M178" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N178" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M178" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -22894,7 +22884,7 @@
       </c>
       <c r="Q178" s="2"/>
       <c r="R178" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="S178" t="s" s="2">
         <v>78</v>
@@ -22936,7 +22926,7 @@
         <v>78</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>88</v>
@@ -22954,7 +22944,7 @@
         <v>78</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>78</v>
@@ -22965,10 +22955,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B179" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22994,10 +22984,10 @@
         <v>102</v>
       </c>
       <c r="L179" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M179" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -23021,7 +23011,7 @@
         <v>78</v>
       </c>
       <c r="W179" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="X179" t="s" s="2">
         <v>78</v>
@@ -23048,7 +23038,7 @@
         <v>78</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -23066,7 +23056,7 @@
         <v>78</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>78</v>
@@ -23077,10 +23067,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23103,16 +23093,16 @@
         <v>89</v>
       </c>
       <c r="K180" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L180" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="L180" t="s" s="2">
+      <c r="M180" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M180" t="s" s="2">
+      <c r="N180" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -23142,25 +23132,25 @@
       </c>
       <c r="Y180" s="2"/>
       <c r="Z180" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AA180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF180" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AA180" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB180" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC180" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD180" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE180" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF180" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>79</v>
@@ -23172,27 +23162,27 @@
         <v>150</v>
       </c>
       <c r="AJ180" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AK180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL180" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AK180" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL180" t="s" s="2">
+      <c r="AM180" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN180" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="AM180" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN180" t="s" s="2">
-        <v>506</v>
       </c>
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23301,10 +23291,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23415,10 +23405,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23441,19 +23431,19 @@
         <v>89</v>
       </c>
       <c r="K183" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L183" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="L183" t="s" s="2">
+      <c r="M183" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M183" t="s" s="2">
+      <c r="N183" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="N183" t="s" s="2">
+      <c r="O183" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>78</v>
@@ -23502,7 +23492,7 @@
         <v>78</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -23520,21 +23510,21 @@
         <v>78</v>
       </c>
       <c r="AL183" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AM183" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN183" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AM183" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN183" t="s" s="2">
-        <v>542</v>
       </c>
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23560,65 +23550,65 @@
         <v>167</v>
       </c>
       <c r="L184" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M184" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M184" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="P184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q184" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="P184" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q184" t="s" s="2">
+      <c r="R184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X184" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="Y184" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="R184" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S184" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T184" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U184" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V184" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W184" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X184" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y184" t="s" s="2">
+      <c r="Z184" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="Z184" t="s" s="2">
+      <c r="AA184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF184" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AA184" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB184" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC184" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD184" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE184" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF184" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
@@ -23636,21 +23626,21 @@
         <v>78</v>
       </c>
       <c r="AL184" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AM184" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN184" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AM184" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN184" t="s" s="2">
-        <v>552</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23676,16 +23666,16 @@
         <v>102</v>
       </c>
       <c r="L185" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M185" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="M185" t="s" s="2">
+      <c r="N185" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O185" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O185" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>78</v>
@@ -23734,7 +23724,7 @@
         <v>78</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
@@ -23752,21 +23742,21 @@
         <v>78</v>
       </c>
       <c r="AL185" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AM185" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN185" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AM185" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN185" t="s" s="2">
-        <v>559</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23792,16 +23782,16 @@
         <v>130</v>
       </c>
       <c r="L186" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M186" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="M186" t="s" s="2">
+      <c r="N186" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="N186" t="s" s="2">
+      <c r="O186" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="O186" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>78</v>
@@ -23850,16 +23840,16 @@
         <v>78</v>
       </c>
       <c r="AF186" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AG186" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH186" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI186" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AG186" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH186" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI186" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>100</v>
@@ -23868,21 +23858,21 @@
         <v>78</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AM186" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23908,16 +23898,16 @@
         <v>167</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M187" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M187" t="s" s="2">
+      <c r="N187" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N187" t="s" s="2">
+      <c r="O187" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>78</v>
@@ -23966,7 +23956,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -23984,21 +23974,21 @@
         <v>78</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AM187" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24021,16 +24011,16 @@
         <v>89</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="L188" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M188" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="M188" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="N188" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -24060,7 +24050,7 @@
       </c>
       <c r="Y188" s="2"/>
       <c r="Z188" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>78</v>
@@ -24078,7 +24068,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24090,27 +24080,27 @@
         <v>150</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AK188" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24219,10 +24209,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -24333,10 +24323,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -24359,19 +24349,19 @@
         <v>89</v>
       </c>
       <c r="K191" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L191" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="L191" t="s" s="2">
+      <c r="M191" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M191" t="s" s="2">
+      <c r="N191" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="N191" t="s" s="2">
+      <c r="O191" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>78</v>
@@ -24420,7 +24410,7 @@
         <v>78</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
@@ -24438,21 +24428,21 @@
         <v>78</v>
       </c>
       <c r="AL191" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AM191" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN191" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AM191" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN191" t="s" s="2">
-        <v>542</v>
       </c>
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -24478,65 +24468,65 @@
         <v>167</v>
       </c>
       <c r="L192" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M192" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M192" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="P192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q192" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="P192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q192" t="s" s="2">
+      <c r="R192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X192" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="Y192" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="R192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X192" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y192" t="s" s="2">
+      <c r="Z192" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="Z192" t="s" s="2">
+      <c r="AA192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF192" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AA192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF192" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
@@ -24554,21 +24544,21 @@
         <v>78</v>
       </c>
       <c r="AL192" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AM192" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN192" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AM192" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN192" t="s" s="2">
-        <v>552</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -24594,16 +24584,16 @@
         <v>102</v>
       </c>
       <c r="L193" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M193" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="M193" t="s" s="2">
+      <c r="N193" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O193" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>78</v>
@@ -24652,7 +24642,7 @@
         <v>78</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>79</v>
@@ -24670,21 +24660,21 @@
         <v>78</v>
       </c>
       <c r="AL193" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AM193" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN193" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AM193" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN193" t="s" s="2">
-        <v>559</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24710,16 +24700,16 @@
         <v>130</v>
       </c>
       <c r="L194" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M194" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="M194" t="s" s="2">
+      <c r="N194" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="N194" t="s" s="2">
+      <c r="O194" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="O194" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>78</v>
@@ -24768,16 +24758,16 @@
         <v>78</v>
       </c>
       <c r="AF194" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AG194" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH194" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI194" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AG194" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH194" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI194" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="AJ194" t="s" s="2">
         <v>100</v>
@@ -24786,21 +24776,21 @@
         <v>78</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24826,16 +24816,16 @@
         <v>167</v>
       </c>
       <c r="L195" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M195" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M195" t="s" s="2">
+      <c r="N195" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N195" t="s" s="2">
+      <c r="O195" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O195" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>78</v>
@@ -24884,7 +24874,7 @@
         <v>78</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
@@ -24902,21 +24892,21 @@
         <v>78</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AM195" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24939,13 +24929,13 @@
         <v>78</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="L196" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M196" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -24996,7 +24986,7 @@
         <v>78</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
@@ -25011,10 +25001,10 @@
         <v>100</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>78</v>
@@ -25025,10 +25015,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25137,10 +25127,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -25251,14 +25241,14 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
@@ -25280,16 +25270,16 @@
         <v>109</v>
       </c>
       <c r="L199" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M199" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="M199" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="N199" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>78</v>
@@ -25338,7 +25328,7 @@
         <v>78</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
@@ -25356,7 +25346,7 @@
         <v>78</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AM199" t="s" s="2">
         <v>78</v>
@@ -25367,10 +25357,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -25396,13 +25386,13 @@
         <v>102</v>
       </c>
       <c r="L200" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M200" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="M200" t="s" s="2">
-        <v>716</v>
-      </c>
       <c r="N200" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -25452,7 +25442,7 @@
         <v>78</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
@@ -25467,24 +25457,24 @@
         <v>100</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -25507,13 +25497,13 @@
         <v>78</v>
       </c>
       <c r="K201" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="L201" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="L201" t="s" s="2">
+      <c r="M201" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="M201" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
@@ -25564,7 +25554,7 @@
         <v>78</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>79</v>
@@ -25579,16 +25569,16 @@
         <v>100</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AL201" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="AM201" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN201" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="AM201" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN201" t="s" s="2">
-        <v>723</v>
       </c>
     </row>
   </sheetData>
